--- a/AS5048_angel/数据.xlsx
+++ b/AS5048_angel/数据.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25967" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="摆动（±30°）" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
   <si>
     <t>序号</t>
   </si>
@@ -733,31 +733,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr defTabSz="914400">
-              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>AS5048读取角度</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -767,20 +742,29 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.140855614973262"/>
-          <c:y val="0.18546511627907"/>
-          <c:w val="0.842967914438503"/>
-          <c:h val="0.677403100775194"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="marker"/>
         <c:varyColors val="0"/>
@@ -789,7 +773,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>'摆动（±30°）'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -825,10 +809,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$77</c:f>
+              <c:f>'摆动（±30°）'!$A$2:$A$123</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="122"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1056,243 +1040,519 @@
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>122</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$77</c:f>
+              <c:f>'摆动（±30°）'!$B$2:$B$123</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="122"/>
                 <c:pt idx="0">
-                  <c:v>0.28</c:v>
+                  <c:v>25.18</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.15</c:v>
+                  <c:v>21.48</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>18.28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.52</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.09</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-3.64</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-10.45</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-14.43</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-18.67</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-22.69</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-27.39</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-23.2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-18.78</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-14.52</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-10.65</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-7.18</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-4.24</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.24</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.98</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.13</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.75</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>14.19</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>17.86</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>21.42</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>24.87</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>21.48</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>18.34</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>14.37</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>10.04</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6.32</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.07</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-3.62</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-6.89</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-10.34</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-14.39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-18.65</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-22.52</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-27.02</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-22.8</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-18.94</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-14.43</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-10.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-7.14</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-4.04</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.21</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6.17</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9.68</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>14.26</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>18.01</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>21.46</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>24.8</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>21.51</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18.28</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>14.56</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3.05</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-0.19</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-3.49</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-10.34</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-14.41</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-18.65</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-22.47</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-27.39</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-22.82</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-18.96</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-14.52</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-10.54</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>-7.16</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>-3.91</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>-0.35</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>3.01</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>9.79</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>13.82</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>18.03</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>21.18</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>25.22</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>21.53</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>18.28</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>10.21</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6.28</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>3.16</c:v>
+                </c:pt>
+                <c:pt idx="91">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>359.95</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>359.95</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>359.93</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.21</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>356.57</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>355.1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>355.16</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>354.74</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>353.56</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>353.25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>350.52</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>346.55</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>343.38</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>339.69</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>334.33</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>326.42</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>321.78</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>316.75</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>310.93</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>306.58</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>301.57</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>298.41</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>296.23</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>294.89</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>294.08</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>292.45</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>290.39</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>288.72</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>286.69</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>284.28</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>283.14</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>279.82</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>276.89</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>276.21</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>278.41</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>281.11</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>282.23</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>276.78</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>270.32</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>260.9</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>249.82</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>241.98</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>229.48</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>223.94</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>219.3</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>217.57</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>213.85</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>212.6</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>212.36</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>213</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>216.82</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>219.7</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>219.66</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>219.88</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>219.96</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>219.7</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>219.59</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>219.88</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>219.79</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>219.7</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>219.48</c:v>
+                <c:pt idx="92">
+                  <c:v>-3.38</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>-10.15</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>-14.67</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>-18.56</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>-22.91</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>-27</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>-23.04</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>-18.78</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>-14.39</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>-10.52</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>-7.25</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>-3.91</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>-0.28</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>3.03</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.95</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>9.79</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>13.99</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>18.01</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>21.2</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>25.29</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>21.62</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>18.25</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>10.12</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>6.41</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>3.09</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>-0.28</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>-3.4</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>-7.11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1307,11 +1567,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="367764200"/>
-        <c:axId val="974448909"/>
+        <c:axId val="27661631"/>
+        <c:axId val="410434951"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="367764200"/>
+        <c:axId val="27661631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1330,48 +1590,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr defTabSz="914400">
-                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>序号</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.91153743315508"/>
-              <c:y val="0.925193798449612"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1408,12 +1626,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="974448909"/>
+        <c:crossAx val="410434951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="974448909"/>
+        <c:axId val="410434951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1432,48 +1650,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr defTabSz="914400">
-                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>角度</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.0362299465240642"/>
-              <c:y val="0.183856589147287"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1510,7 +1686,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="367764200"/>
+        <c:crossAx val="27661631"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1528,81 +1704,8 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr lang="zh-CN"/>
-      </a:pPr>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr defTabSz="914400">
-              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>AS5048读取角度</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
+    <c:legend>
+      <c:legendPos val="b"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -1612,716 +1715,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="marker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>角度</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$70</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>31</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>42</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>44</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>53</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>62</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>63</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>66</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>67</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>68</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>69</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$2:$D$70</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="69"/>
-                <c:pt idx="0">
-                  <c:v>359.97</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.19</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>359.89</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.21</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.58</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.41</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.74</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.48</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10.39</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>12.23</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14.26</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>16.23</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.85</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>22.91</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>24.96</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>26.85</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>27.59</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>30.6</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>31.88</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>35.09</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>39.61</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>42.93</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>42.97</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>42.03</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>44.03</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>47.81</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>50.99</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>52.95</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>54.31</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>55.45</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>55.92</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>57.32</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>58.49</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>60.24</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>60.57</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>62.64</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>63.45</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>64.46</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>65.72</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>66.7</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>69.23</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>73.3</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>77.08</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>82.02</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>86.72</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>92.04</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>98.15</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>104.54</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>112.12</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>116.96</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>120.21</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>122.1</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>124.1</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>125.68</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>126.71</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>127.59</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>130.49</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>134.51</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>138.38</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>141.92</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>142.22</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>143.67</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>143.94</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>145.54</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>147.04</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>147.83</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="939560656"/>
-        <c:axId val="329273597"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="939560656"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr defTabSz="914400">
-                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>序号</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.907802631578947"/>
-              <c:y val="0.883333333333333"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="329273597"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="329273597"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="90200"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr defTabSz="914400">
-                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>角度</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="0.0273684210526316"/>
-              <c:y val="0.144722222222222"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="939560656"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="15000"/>
-              <a:lumOff val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:round/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -2359,46 +1772,6 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2974,599 +2347,33 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10172">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:noFill/>
-        <a:round/>
-      </a:ln>
-      <a:effectLst/>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-      <a:effectLst/>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="90200"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>119380</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>116840</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>424180</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>170180</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>170180</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="图表 3"/>
+        <xdr:cNvPr id="3" name="图表 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5674360" y="8712200"/>
-        <a:ext cx="4749800" cy="3276600"/>
+        <a:off x="7213600" y="718820"/>
+        <a:ext cx="4826000" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>322580</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>210820</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="图表 4"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="10815320" y="8867140"/>
-        <a:ext cx="4826000" cy="2743200"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5251,19 +4058,1004 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:B123"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>25.18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>21.48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>18.28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>14.52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6.26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>-3.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>-10.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>-14.43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>-18.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>-22.69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>-27.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>-23.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>-18.78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>-14.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>-10.65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>-7.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>-4.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>17.86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>21.42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>24.87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>21.48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>18.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>14.37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>10.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>-6.89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>-10.34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>-14.39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>-18.65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>-22.52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>-27.02</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>-22.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>-18.94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>-14.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>-7.14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>21.46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>21.51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>18.28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>-3.49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>-10.34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>-14.41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>-18.65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>-22.47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>-27.39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>-22.82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>-18.96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>-14.52</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>-10.54</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>-7.16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>9.79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>13.82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>18.03</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>21.18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>25.22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>21.53</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>18.28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>10.21</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>-3.38</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>-10.15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>-14.67</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>-18.56</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>-22.91</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>-23.04</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>-18.78</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>-14.39</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>-10.52</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>-7.25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>9.79</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>18.01</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>25.29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>21.62</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>-7.11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
